--- a/Projeto de Software e Segurança da Informação - 2026/Projeto de Software/Aula07-HerançaPolimorfismo/Projeto de Classe (UML) - Herança.xlsx
+++ b/Projeto de Software e Segurança da Informação - 2026/Projeto de Software/Aula07-HerançaPolimorfismo/Projeto de Classe (UML) - Herança.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunocmc\Documents\UMC\Projeto de Software e Segurança da Informação - 2026\Projeto de Software\Aula07-HerançaPolimorfismo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E270F52-EA51-469D-87E2-9A319A408EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8783892A-2E65-41F2-BAC5-89C88271BB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C745455B-B4B6-4675-A588-66F7A2F66F4C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>Peixe</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>+ exibirInfo(): void</t>
+  </si>
+  <si>
+    <t>Animal</t>
   </si>
 </sst>
 </file>
@@ -156,25 +159,25 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -497,83 +500,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F94FD44-01CE-4C63-99EF-B1761CA53137}">
-  <dimension ref="B1:F8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:F11"/>
+  <sheetFormatPr defaultRowHeight="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.6640625" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="30.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="7"/>
+    <col min="4" max="4" width="30.6640625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="7"/>
+    <col min="6" max="6" width="30.6640625" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:6" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="3" t="s">
+    <row r="1" spans="2:6" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:6" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D5" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="2:6" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D9" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="6" t="s">
+    <row r="10" spans="2:6" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="2" t="s">
+    <row r="11" spans="2:6" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
